--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="江戸川区" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="江戸川区" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -485,10 +485,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>35.6726</v>
+        <v>35.6646</v>
       </c>
       <c r="E2" t="n">
-        <v>139.8695</v>
+        <v>139.8592</v>
       </c>
       <c r="F2" t="n">
         <v>4</v>
@@ -511,10 +511,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>35.6683</v>
+        <v>35.6635</v>
       </c>
       <c r="E3" t="n">
-        <v>139.881</v>
+        <v>139.8727</v>
       </c>
       <c r="F3" t="n">
         <v>3</v>
@@ -537,10 +537,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>35.6455</v>
+        <v>35.6444</v>
       </c>
       <c r="E4" t="n">
-        <v>139.8886</v>
+        <v>139.8616</v>
       </c>
       <c r="F4" t="n">
         <v>5</v>
@@ -563,10 +563,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>35.6905</v>
+        <v>35.6839</v>
       </c>
       <c r="E5" t="n">
-        <v>139.8785</v>
+        <v>139.8641</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
@@ -589,10 +589,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>35.6962</v>
+        <v>35.6859</v>
       </c>
       <c r="E6" t="n">
-        <v>139.8877</v>
+        <v>139.883</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -615,10 +615,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>35.7012</v>
+        <v>35.6933</v>
       </c>
       <c r="E7" t="n">
-        <v>139.8974</v>
+        <v>139.8977</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
@@ -641,10 +641,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>35.7077</v>
+        <v>35.706</v>
       </c>
       <c r="E8" t="n">
-        <v>139.9063</v>
+        <v>139.9039</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -670,7 +670,7 @@
         <v>35.7333</v>
       </c>
       <c r="E9" t="n">
-        <v>139.8819</v>
+        <v>139.882</v>
       </c>
       <c r="F9" t="n">
         <v>2</v>
@@ -693,10 +693,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>35.712</v>
+        <v>35.7174</v>
       </c>
       <c r="E10" t="n">
-        <v>139.8658</v>
+        <v>139.8586</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>35.7022</v>
+        <v>35.7066</v>
       </c>
       <c r="E11" t="n">
-        <v>139.8472</v>
+        <v>139.8427</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -748,7 +748,7 @@
         <v>35.7378</v>
       </c>
       <c r="E12" t="n">
-        <v>139.896</v>
+        <v>139.8959</v>
       </c>
       <c r="F12" t="n">
         <v>2</v>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>35.742</v>
+        <v>35.7421</v>
       </c>
       <c r="E13" t="n">
         <v>139.8839</v>
